--- a/output/企业标签全量表_2026-07-15_v12.2.xlsx
+++ b/output/企业标签全量表_2026-07-15_v12.2.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金融理财</t>
+          <t>金融理财;保险</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>上门</t>
+          <t>上门;SaaS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;智能科技</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;智能科技</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;SaaS;智能硬件</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长护险经办</t>
+          <t>长护险经办;保险;居家护理</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;金融保险</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>认知训练</t>
+          <t>认知训练;SaaS;保险</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;AI;智能硬件</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>认知训练</t>
+          <t>认知训练;SaaS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>长护险经办</t>
+          <t>长护险经办;保险;居家护理</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;AI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>行业展会</t>
+          <t>行业媒体</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2557,12 +2557,12 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;康复辅具</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>行业展会</t>
+          <t>行业媒体;康复器械</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;康复辅具</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>行业展会</t>
+          <t>行业媒体;康复器械</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;消费品</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>行业展会</t>
+          <t>行业媒体;智能硬件</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;养老服务</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>养老膳食</t>
+          <t>养老膳食;居家护理</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>旅居养老</t>
+          <t>持续照料社区</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>居家护理;智能硬件</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>电商;电视购物</t>
+          <t>电商;零售</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>益生菌肠道;骨关节钙</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>电商;私域电商</t>
+          <t>电商;零售</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;康复器械</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;金融保险</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>陪诊</t>
+          <t>陪诊;保险</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;慢病管理</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;智能科技</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>个人护理</t>
+          <t>个人护理;智能硬件</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>认知训练</t>
+          <t>认知训练;SaaS;AI</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>个人护理</t>
+          <t>个人护理;智能硬件</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>养老服务;金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>养老服务;金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>产业资本;养老服务</t>
+          <t>养老服务;产业资本</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品;医疗健康</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件;慢病管理</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>电视购物</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;慢病管理</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;慢病管理</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;智能硬件</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>电商;电视购物</t>
+          <t>电商;零售</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>私域电商</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>医疗器械;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>电商;电视购物</t>
+          <t>电商;零售</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>糖尿病管理;SaaS;慢病管理</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>益生菌肠道</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>助听辅具;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;智能硬件;慢病管理</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;消费品</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>糖尿病管理;AI;智能硬件</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>护理床;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;智能硬件</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -11544,12 +11544,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -11673,12 +11673,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>护理床;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>广场舞社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>私域电商</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -12232,12 +12232,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>糖尿病管理;SaaS</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -12748,12 +12748,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>广场舞社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>养老运营</t>
+          <t>养老运营;慢病管理</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>护理床;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -13651,12 +13651,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>护士上门;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>电商服务</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>营养食品</t>
+          <t>营养食品;慢病管理</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -14210,12 +14210,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>广场舞社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>电商服务</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -14601,12 +14601,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>益生菌肠道</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -14902,12 +14902,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>消费品;康复辅具</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>电商服务</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -15461,12 +15461,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -15633,12 +15633,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>护士上门;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>护士上门;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -16192,12 +16192,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>家政生活服务</t>
+          <t>家政生活服务;居家护理</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>护士上门;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -16450,12 +16450,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>护士上门;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>电商;私域电商</t>
+          <t>电商;零售</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -16837,12 +16837,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>营养食品</t>
+          <t>营养食品;慢病管理</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -17157,12 +17157,12 @@
       <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;医疗健康</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;慢病管理</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -17196,12 +17196,12 @@
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>用药管理</t>
+          <t>用药管理;保险</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -17454,12 +17454,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>养老信息平台</t>
+          <t>养老信息平台;AI;慢病管理</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>旅居养老</t>
+          <t>持续照料社区</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -18013,12 +18013,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>长护险经办</t>
+          <t>长护险经办;居家护理</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -18889,12 +18889,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;慢病管理</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -18975,12 +18975,12 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;金融保险</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>持续照料社区</t>
+          <t>持续照料社区;保险</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -19018,12 +19018,12 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;金融保险</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>持续照料社区</t>
+          <t>持续照料社区;保险</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -19108,12 +19108,12 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>消费品;金融保险;养老服务</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>智能硬件;保险;居家护理</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -19323,12 +19323,12 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;养老服务</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>护理床;居家护理</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>听力训练</t>
+          <t>助听器</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -19538,12 +19538,12 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;康复辅具</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -19581,12 +19581,12 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -19757,12 +19757,12 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;康复辅具</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>资讯门户</t>
+          <t>资讯门户;康复器械</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -19972,12 +19972,12 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;金融保险</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老咨询;保险</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>旅居养老</t>
+          <t>持续照料社区</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -20717,12 +20717,12 @@
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -20795,12 +20795,12 @@
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;保险</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -20873,12 +20873,12 @@
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>居家医疗;保险</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -20917,7 +20917,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;慢病管理</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -21068,12 +21068,12 @@
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>居家护理;远程医疗;保险</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -21146,12 +21146,12 @@
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;养老服务</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>养老咨询;居家护理</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>并购投资</t>
+          <t>产业基金</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -21920,7 +21920,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -22235,12 +22235,12 @@
       <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -22478,7 +22478,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>医疗器械;慢病管理</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -22806,7 +22806,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;远程医疗</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>活动社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -23731,7 +23731,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -23765,12 +23765,12 @@
       <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;保险</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>就医导航</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -24163,12 +24163,12 @@
       <c r="B560" t="inlineStr"/>
       <c r="C560" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;金融保险;消费品</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;保险;智能硬件</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -24362,12 +24362,12 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;保险</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -24674,12 +24674,12 @@
       <c r="B573" t="inlineStr"/>
       <c r="C573" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;医疗健康</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>VC;远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -24873,12 +24873,12 @@
       <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;智能科技</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>VC;SaaS</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -24917,7 +24917,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>并购投资</t>
+          <t>产业基金</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>并购投资</t>
+          <t>产业基金</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -25361,12 +25361,12 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>就业</t>
+          <t>就业;SaaS</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -25439,12 +25439,12 @@
       <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>就业</t>
+          <t>就业;AI;远程医疗</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -26196,12 +26196,12 @@
       <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>健身</t>
+          <t>健身;跌倒监测</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>活动社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -26313,12 +26313,12 @@
       <c r="B614" t="inlineStr"/>
       <c r="C614" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;智能硬件</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -26552,7 +26552,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -26859,12 +26859,12 @@
       <c r="B628" t="inlineStr"/>
       <c r="C628" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>心理健康;保险</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;远程医疗</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>尿失禁</t>
+          <t>尿失禁;智能硬件</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -27210,12 +27210,12 @@
       <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -27249,12 +27249,12 @@
       <c r="B638" t="inlineStr"/>
       <c r="C638" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;智能科技</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>个性化营养</t>
+          <t>个性化营养;AI</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -27288,12 +27288,12 @@
       <c r="B639" t="inlineStr"/>
       <c r="C639" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>保健品</t>
+          <t>保健品;慢病管理</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -27717,12 +27717,12 @@
       <c r="B650" t="inlineStr"/>
       <c r="C650" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -27795,12 +27795,12 @@
       <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -27873,12 +27873,12 @@
       <c r="B654" t="inlineStr"/>
       <c r="C654" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>专业护理</t>
+          <t>专业护理;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -28224,7 +28224,7 @@
       <c r="B663" t="inlineStr"/>
       <c r="C663" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -28268,7 +28268,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -28302,12 +28302,12 @@
       <c r="B665" t="inlineStr"/>
       <c r="C665" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>文娱</t>
+          <t>文娱;AI</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -28380,7 +28380,7 @@
       <c r="B667" t="inlineStr"/>
       <c r="C667" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -28575,12 +28575,12 @@
       <c r="B672" t="inlineStr"/>
       <c r="C672" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;AI</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -28614,12 +28614,12 @@
       <c r="B673" t="inlineStr"/>
       <c r="C673" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>安宁疗护</t>
+          <t>安宁疗护;居家护理</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -28653,12 +28653,12 @@
       <c r="B674" t="inlineStr"/>
       <c r="C674" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>居家护理;远程医疗</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -28848,7 +28848,7 @@
       <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -29004,12 +29004,12 @@
       <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;AI</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS;AI</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -29160,12 +29160,12 @@
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>护理者支持</t>
+          <t>护理者支持;SaaS</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>听力训练</t>
+          <t>助听器</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -29364,7 +29364,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>更年期</t>
+          <t>更年期;远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>尿失禁</t>
+          <t>尿失禁;智能硬件</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -29632,7 +29632,7 @@
       <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
-          <t>养老服务;金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -29788,12 +29788,12 @@
       <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>膳食配送</t>
+          <t>膳食配送;慢病管理</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -29866,12 +29866,12 @@
       <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>兴趣社群</t>
+          <t>兴趣社群;AI</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -29910,7 +29910,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -30065,7 +30065,7 @@
       <c r="B710" t="inlineStr"/>
       <c r="C710" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -30104,12 +30104,12 @@
       <c r="B711" t="inlineStr"/>
       <c r="C711" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>医疗健康</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -30221,12 +30221,12 @@
       <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -30299,12 +30299,12 @@
       <c r="B716" t="inlineStr"/>
       <c r="C716" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>心理健康;保险</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -30533,12 +30533,12 @@
       <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>保健品</t>
+          <t>保健品;慢病管理</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -30611,12 +30611,12 @@
       <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>心理健康;保险</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -30650,12 +30650,12 @@
       <c r="B725" t="inlineStr"/>
       <c r="C725" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -30689,12 +30689,12 @@
       <c r="B726" t="inlineStr"/>
       <c r="C726" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>远程护理</t>
+          <t>远程护理;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -30888,12 +30888,12 @@
       <c r="B731" t="inlineStr"/>
       <c r="C731" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;金融保险</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>家政生活服务</t>
+          <t>家政生活服务;保险;居家护理</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -30927,12 +30927,12 @@
       <c r="B732" t="inlineStr"/>
       <c r="C732" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;保险</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -31092,7 +31092,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -31477,7 +31477,7 @@
       <c r="B746" t="inlineStr"/>
       <c r="C746" t="inlineStr">
         <is>
-          <t>医疗健康;食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -31516,7 +31516,7 @@
       <c r="B747" t="inlineStr"/>
       <c r="C747" t="inlineStr">
         <is>
-          <t>医疗健康;消费品</t>
+          <t>消费品;医疗健康</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>眼镜</t>
+          <t>眼镜;智能硬件</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -31789,12 +31789,12 @@
       <c r="B754" t="inlineStr"/>
       <c r="C754" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;医疗健康</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;远程医疗</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -31867,12 +31867,12 @@
       <c r="B756" t="inlineStr"/>
       <c r="C756" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;远程医疗;居家护理</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -31950,7 +31950,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>听力训练</t>
+          <t>助听器</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -32257,12 +32257,12 @@
       <c r="B766" t="inlineStr"/>
       <c r="C766" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -32296,12 +32296,12 @@
       <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;养老服务</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>养老信息平台</t>
+          <t>养老信息平台;居家护理</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -32413,12 +32413,12 @@
       <c r="B770" t="inlineStr"/>
       <c r="C770" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;智能科技</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>金融理财</t>
+          <t>金融理财;SaaS</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -32608,12 +32608,12 @@
       <c r="B775" t="inlineStr"/>
       <c r="C775" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;慢病管理;居家护理</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -32846,12 +32846,12 @@
       <c r="B781" t="inlineStr"/>
       <c r="C781" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;智能硬件</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -32963,7 +32963,7 @@
       <c r="B784" t="inlineStr"/>
       <c r="C784" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -33119,12 +33119,12 @@
       <c r="B788" t="inlineStr"/>
       <c r="C788" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>上门</t>
+          <t>上门;远程医疗</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -33158,12 +33158,12 @@
       <c r="B789" t="inlineStr"/>
       <c r="C789" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;保险</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -33197,12 +33197,12 @@
       <c r="B790" t="inlineStr"/>
       <c r="C790" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>专业护理</t>
+          <t>专业护理;慢病管理;居家护理</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>活动社交</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -33435,12 +33435,12 @@
       <c r="B796" t="inlineStr"/>
       <c r="C796" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>认知筛查</t>
+          <t>认知筛查;智能硬件</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -33552,12 +33552,12 @@
       <c r="B799" t="inlineStr"/>
       <c r="C799" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -33630,12 +33630,12 @@
       <c r="B801" t="inlineStr"/>
       <c r="C801" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;金融保险</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;保险</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -33786,12 +33786,12 @@
       <c r="B805" t="inlineStr"/>
       <c r="C805" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;金融保险</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>个性化营养</t>
+          <t>个性化营养;保险</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -33825,12 +33825,12 @@
       <c r="B806" t="inlineStr"/>
       <c r="C806" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;智能科技;金融保险</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>膳食配送</t>
+          <t>膳食配送;SaaS;保险</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -33908,7 +33908,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;慢病管理</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -34020,12 +34020,12 @@
       <c r="B811" t="inlineStr"/>
       <c r="C811" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -34137,12 +34137,12 @@
       <c r="B814" t="inlineStr"/>
       <c r="C814" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>远程护理</t>
+          <t>远程护理;远程医疗</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -34176,12 +34176,12 @@
       <c r="B815" t="inlineStr"/>
       <c r="C815" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>文娱</t>
+          <t>文娱;AI</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -34293,12 +34293,12 @@
       <c r="B818" t="inlineStr"/>
       <c r="C818" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;SaaS</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>更年期</t>
+          <t>更年期;远程医疗</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>健康管理</t>
+          <t>健康管理;慢病管理</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -34683,12 +34683,12 @@
       <c r="B828" t="inlineStr"/>
       <c r="C828" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助行器;智能硬件</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -34839,12 +34839,12 @@
       <c r="B832" t="inlineStr"/>
       <c r="C832" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;SaaS;跌倒监测</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -35077,12 +35077,12 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -35467,7 +35467,7 @@
       <c r="B848" t="inlineStr"/>
       <c r="C848" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -35506,12 +35506,12 @@
       <c r="B849" t="inlineStr"/>
       <c r="C849" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>健康管理</t>
+          <t>健康管理;居家护理</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
@@ -35740,12 +35740,12 @@
       <c r="B855" t="inlineStr"/>
       <c r="C855" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>SDOH;SaaS</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -35974,12 +35974,12 @@
       <c r="B861" t="inlineStr"/>
       <c r="C861" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;AI</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;保险</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -36095,12 +36095,12 @@
       <c r="B864" t="inlineStr"/>
       <c r="C864" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;AI</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -36173,12 +36173,12 @@
       <c r="B866" t="inlineStr"/>
       <c r="C866" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>慢病管理;远程医疗;智能硬件</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -36412,7 +36412,7 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>糖尿病管理;慢病管理</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -36446,12 +36446,12 @@
       <c r="B873" t="inlineStr"/>
       <c r="C873" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;AI</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -36719,7 +36719,7 @@
       <c r="B880" t="inlineStr"/>
       <c r="C880" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -36758,12 +36758,12 @@
       <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;远程医疗;保险</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -36884,7 +36884,7 @@
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -36918,12 +36918,12 @@
       <c r="B885" t="inlineStr"/>
       <c r="C885" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>就医导航</t>
+          <t>远程医疗;AI;慢病管理</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -37035,12 +37035,12 @@
       <c r="B888" t="inlineStr"/>
       <c r="C888" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>心理健康;AI</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -37230,12 +37230,12 @@
       <c r="B893" t="inlineStr"/>
       <c r="C893" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>居家医疗;保险</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -37554,12 +37554,12 @@
       <c r="B901" t="inlineStr"/>
       <c r="C901" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>远程护理</t>
+          <t>远程护理;SaaS;远程医疗</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -38222,7 +38222,7 @@
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>长护险经办</t>
+          <t>长护险经办;保险</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
@@ -38373,12 +38373,12 @@
       <c r="B922" t="inlineStr"/>
       <c r="C922" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>消费品;养老服务</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>智能硬件;居家护理</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -38416,7 +38416,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>居家医疗;慢病管理</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -39025,7 +39025,7 @@
       <c r="B938" t="inlineStr"/>
       <c r="C938" t="inlineStr">
         <is>
-          <t>养老服务;金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -39142,12 +39142,12 @@
       <c r="B941" t="inlineStr"/>
       <c r="C941" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>诊所;保险</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -39185,12 +39185,12 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -39272,7 +39272,7 @@
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>康复医疗;远程医疗</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -39393,7 +39393,7 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>安宁疗护</t>
+          <t>安宁疗护;慢病管理</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>专业护理</t>
+          <t>专业护理;居家护理</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -39548,12 +39548,12 @@
       <c r="B951" t="inlineStr"/>
       <c r="C951" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>安宁疗护</t>
+          <t>安宁疗护;居家护理</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
@@ -39670,7 +39670,7 @@
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>家政生活服务</t>
+          <t>家政生活服务;居家护理</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
@@ -39899,12 +39899,12 @@
       <c r="B960" t="inlineStr"/>
       <c r="C960" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;智能科技</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>金融理财</t>
+          <t>金融理财;SaaS;保险</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
@@ -39938,7 +39938,7 @@
       <c r="B961" t="inlineStr"/>
       <c r="C961" t="inlineStr">
         <is>
-          <t>养老服务;医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
@@ -40021,7 +40021,7 @@
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS;AI</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
@@ -40055,12 +40055,12 @@
       <c r="B964" t="inlineStr"/>
       <c r="C964" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;金融保险</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;AI;保险</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
@@ -40098,7 +40098,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -40254,7 +40254,7 @@
       <c r="B969" t="inlineStr"/>
       <c r="C969" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -40492,12 +40492,12 @@
       <c r="B975" t="inlineStr"/>
       <c r="C975" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>用药提醒</t>
+          <t>用药提醒;保险;慢病管理</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
@@ -40531,12 +40531,12 @@
       <c r="B976" t="inlineStr"/>
       <c r="C976" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
@@ -40613,12 +40613,12 @@
       <c r="B978" t="inlineStr"/>
       <c r="C978" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -40652,12 +40652,12 @@
       <c r="B979" t="inlineStr"/>
       <c r="C979" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -40808,12 +40808,12 @@
       <c r="B983" t="inlineStr"/>
       <c r="C983" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;消费品</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;智能硬件</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -41046,12 +41046,12 @@
       <c r="B989" t="inlineStr"/>
       <c r="C989" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>消费品;智能科技</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>服装鞋帽;跌倒监测</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -41163,12 +41163,12 @@
       <c r="B992" t="inlineStr"/>
       <c r="C992" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;智能科技</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>保险科技;SaaS;保险</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -41397,12 +41397,12 @@
       <c r="B998" t="inlineStr"/>
       <c r="C998" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人;智能硬件</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -41436,12 +41436,12 @@
       <c r="B999" t="inlineStr"/>
       <c r="C999" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -41514,12 +41514,12 @@
       <c r="B1001" t="inlineStr"/>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;远程医疗;智能硬件</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -41553,12 +41553,12 @@
       <c r="B1002" t="inlineStr"/>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>消费品;医疗健康</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>智能硬件;远程医疗</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -41597,7 +41597,7 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -41709,12 +41709,12 @@
       <c r="B1006" t="inlineStr"/>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;消费品</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>陪伴社交;智能硬件</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -41748,12 +41748,12 @@
       <c r="B1007" t="inlineStr"/>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;跌倒监测</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -42216,12 +42216,12 @@
       <c r="B1019" t="inlineStr"/>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>用药管理</t>
+          <t>用药管理;SaaS</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -42333,12 +42333,12 @@
       <c r="B1022" t="inlineStr"/>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>产业资本;智能科技</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>养老信息平台</t>
+          <t>养老信息平台;SaaS</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -42411,12 +42411,12 @@
       <c r="B1024" t="inlineStr"/>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;智能科技</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;跌倒监测</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -42450,12 +42450,12 @@
       <c r="B1025" t="inlineStr"/>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;金融保险</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;SaaS;保险</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
@@ -42528,12 +42528,12 @@
       <c r="B1027" t="inlineStr"/>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;消费品</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>远程监护</t>
+          <t>远程监护;SaaS;智能硬件</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -42567,12 +42567,12 @@
       <c r="B1028" t="inlineStr"/>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
@@ -42606,12 +42606,12 @@
       <c r="B1029" t="inlineStr"/>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>远程监护</t>
+          <t>远程监护;智能硬件</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
@@ -42645,12 +42645,12 @@
       <c r="B1030" t="inlineStr"/>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;金融保险</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;SaaS;保险</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -42996,12 +42996,12 @@
       <c r="B1039" t="inlineStr"/>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>机器人;智能硬件</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
@@ -43113,12 +43113,12 @@
       <c r="B1042" t="inlineStr"/>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;养老服务</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>长护险经办</t>
+          <t>长护险经办;保险;居家护理</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
@@ -43269,12 +43269,12 @@
       <c r="B1046" t="inlineStr"/>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品;智能科技</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
@@ -43347,12 +43347,12 @@
       <c r="B1048" t="inlineStr"/>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
@@ -43425,12 +43425,12 @@
       <c r="B1050" t="inlineStr"/>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件</t>
         </is>
       </c>
       <c r="E1050" t="inlineStr">
@@ -43503,12 +43503,12 @@
       <c r="B1052" t="inlineStr"/>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>个性化营养</t>
+          <t>个性化营养;SaaS;慢病管理</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
@@ -43659,12 +43659,12 @@
       <c r="B1056" t="inlineStr"/>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;智能硬件</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
@@ -43750,7 +43750,7 @@
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
@@ -43793,7 +43793,7 @@
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>养老服务;文娱社交;智能科技</t>
+          <t>养老服务;智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -44175,7 +44175,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>养老服务;文娱社交;智能科技</t>
+          <t>养老服务;智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -44304,7 +44304,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -44481,7 +44481,7 @@
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
@@ -44567,7 +44567,7 @@
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
@@ -44691,7 +44691,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
@@ -44734,7 +44734,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -44868,7 +44868,7 @@
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>人形机器人</t>
+          <t>人形机器人;SaaS</t>
         </is>
       </c>
       <c r="E1084" t="inlineStr">
@@ -44906,7 +44906,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>康复辅具;智能科技;消费品</t>
+          <t>康复辅具;消费品;智能科技</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -44992,7 +44992,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -45083,7 +45083,7 @@
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>骨关节钙</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="E1089" t="inlineStr">
@@ -45126,7 +45126,7 @@
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>骨关节钙</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
@@ -45625,7 +45625,7 @@
       <c r="B1102" t="inlineStr"/>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
@@ -45742,12 +45742,12 @@
       <c r="B1105" t="inlineStr"/>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E1105" t="inlineStr">
@@ -45781,12 +45781,12 @@
       <c r="B1106" t="inlineStr"/>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>护理者支持</t>
+          <t>护理者支持;远程医疗</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
@@ -45859,12 +45859,12 @@
       <c r="B1108" t="inlineStr"/>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E1108" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>人形机器人</t>
+          <t>人形机器人;AI</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
@@ -46071,7 +46071,7 @@
       </c>
       <c r="D1113" t="inlineStr">
         <is>
-          <t>人形机器人</t>
+          <t>人形机器人;AI</t>
         </is>
       </c>
       <c r="E1113" t="inlineStr">
@@ -46109,12 +46109,12 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;智能科技;消费品</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;AI;智能硬件</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
@@ -46152,12 +46152,12 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;AI</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -46234,12 +46234,12 @@
       <c r="B1117" t="inlineStr"/>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>居家医疗;居家护理</t>
         </is>
       </c>
       <c r="E1117" t="inlineStr">
@@ -46278,7 +46278,7 @@
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;居家护理</t>
         </is>
       </c>
       <c r="E1118" t="inlineStr">
@@ -46741,12 +46741,12 @@
       <c r="B1130" t="inlineStr"/>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;医疗健康</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>居家护理;远程医疗</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
@@ -47218,7 +47218,7 @@
       </c>
       <c r="D1142" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;慢病管理</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
@@ -47252,12 +47252,12 @@
       <c r="B1143" t="inlineStr"/>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;SaaS</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>用药提醒</t>
+          <t>用药提醒;慢病管理</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="D1153" t="inlineStr">
         <is>
-          <t>药品配送</t>
+          <t>药品配送;慢病管理</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
@@ -48053,12 +48053,12 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;保险</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -48354,12 +48354,12 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;养老服务</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>居家医疗;居家护理</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
@@ -48397,12 +48397,12 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;消费品</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>适老化;智能硬件</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -48440,12 +48440,12 @@
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;远程医疗;智能硬件</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
@@ -48660,7 +48660,7 @@
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>用药提醒</t>
+          <t>用药提醒;慢病管理</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
@@ -48815,12 +48815,12 @@
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;SaaS</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
@@ -48854,12 +48854,12 @@
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>视觉辅助;SaaS;远程医疗</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
@@ -48893,12 +48893,12 @@
       <c r="B1182" t="inlineStr"/>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>用药提醒</t>
+          <t>用药提醒;SaaS;慢病管理</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>就医导航</t>
+          <t>远程医疗;慢病管理</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
@@ -49092,12 +49092,12 @@
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;智能硬件;康复器械</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
@@ -49135,12 +49135,12 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;康复辅具</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;康复器械</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
@@ -49226,7 +49226,7 @@
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>就医导航</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
@@ -49264,12 +49264,12 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;AI</t>
         </is>
       </c>
       <c r="E1191" t="inlineStr">
@@ -49307,12 +49307,12 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;SaaS;慢病管理</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
@@ -49565,7 +49565,7 @@
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -49694,12 +49694,12 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;保险</t>
         </is>
       </c>
       <c r="E1201" t="inlineStr">
@@ -49823,12 +49823,12 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;康复辅具</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>神经调控;康复器械</t>
         </is>
       </c>
       <c r="E1204" t="inlineStr">
@@ -49987,12 +49987,12 @@
       <c r="B1208" t="inlineStr"/>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;医疗健康</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;远程医疗</t>
         </is>
       </c>
       <c r="E1208" t="inlineStr">
@@ -50030,12 +50030,12 @@
       <c r="B1209" t="inlineStr"/>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件</t>
         </is>
       </c>
       <c r="E1209" t="inlineStr">
@@ -50073,12 +50073,12 @@
       <c r="B1210" t="inlineStr"/>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>助听器;智能硬件</t>
         </is>
       </c>
       <c r="E1210" t="inlineStr">
@@ -50151,12 +50151,12 @@
       <c r="B1212" t="inlineStr"/>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1212" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>视觉辅助;智能硬件</t>
         </is>
       </c>
       <c r="E1212" t="inlineStr">
@@ -50190,12 +50190,12 @@
       <c r="B1213" t="inlineStr"/>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1213" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>视觉辅助;智能硬件</t>
         </is>
       </c>
       <c r="E1213" t="inlineStr">
@@ -50229,12 +50229,12 @@
       <c r="B1214" t="inlineStr"/>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>视觉辅助;智能硬件</t>
         </is>
       </c>
       <c r="E1214" t="inlineStr">
@@ -50312,7 +50312,7 @@
       </c>
       <c r="D1216" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>轮椅;康复器械</t>
         </is>
       </c>
       <c r="E1216" t="inlineStr">
@@ -50390,7 +50390,7 @@
       </c>
       <c r="D1218" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1218" t="inlineStr">
@@ -50429,7 +50429,7 @@
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>外骨骼;康复器械</t>
         </is>
       </c>
       <c r="E1219" t="inlineStr">
@@ -50861,12 +50861,12 @@
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
@@ -50939,12 +50939,12 @@
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>养老服务;智能科技</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>护理协调;SaaS;居家护理</t>
         </is>
       </c>
       <c r="E1232" t="inlineStr">
@@ -51099,12 +51099,12 @@
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;医疗健康</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>保险;慢病管理</t>
         </is>
       </c>
       <c r="E1236" t="inlineStr">
@@ -51138,12 +51138,12 @@
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;医疗健康</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>保险;慢病管理</t>
         </is>
       </c>
       <c r="E1237" t="inlineStr">
@@ -51255,12 +51255,12 @@
       <c r="B1240" t="inlineStr"/>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
         <is>
-          <t>体检筛查</t>
+          <t>体检筛查;智能硬件</t>
         </is>
       </c>
       <c r="E1240" t="inlineStr">
@@ -51606,12 +51606,12 @@
       <c r="B1249" t="inlineStr"/>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>康复辅具;消费品;智能科技</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>康复器械;智能硬件;跌倒监测</t>
         </is>
       </c>
       <c r="E1249" t="inlineStr">
@@ -51767,7 +51767,7 @@
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>药品配送</t>
+          <t>药品配送;慢病管理</t>
         </is>
       </c>
       <c r="E1253" t="inlineStr">
@@ -51883,12 +51883,12 @@
       <c r="B1256" t="inlineStr"/>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>食品营养</t>
+          <t>食品营养;医疗健康</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
         <is>
-          <t>膳食配送</t>
+          <t>膳食配送;慢病管理</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
@@ -52039,12 +52039,12 @@
       <c r="B1260" t="inlineStr"/>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;金融保险</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>健康服务平台;保险;慢病管理</t>
         </is>
       </c>
       <c r="E1260" t="inlineStr">
@@ -52078,12 +52078,12 @@
       <c r="B1261" t="inlineStr"/>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1261" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>睡眠监测;跌倒监测</t>
         </is>
       </c>
       <c r="E1261" t="inlineStr">
@@ -52429,12 +52429,12 @@
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技</t>
         </is>
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>心理健康;SaaS</t>
         </is>
       </c>
       <c r="E1270" t="inlineStr">
@@ -52546,12 +52546,12 @@
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;智能科技;消费品</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>视觉辅助;SaaS;智能硬件</t>
         </is>
       </c>
       <c r="E1273" t="inlineStr">
@@ -52590,7 +52590,7 @@
       </c>
       <c r="D1274" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;慢病管理</t>
         </is>
       </c>
       <c r="E1274" t="inlineStr">
@@ -52632,12 +52632,12 @@
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;消费品</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;智能硬件</t>
         </is>
       </c>
       <c r="E1275" t="inlineStr">
@@ -52676,7 +52676,7 @@
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>紧急呼叫;跌倒监测</t>
         </is>
       </c>
       <c r="E1276" t="inlineStr">
@@ -52749,12 +52749,12 @@
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1278" t="inlineStr">
         <is>
-          <t>体检筛查</t>
+          <t>体检筛查;远程医疗;智能硬件</t>
         </is>
       </c>
       <c r="E1278" t="inlineStr">
@@ -52792,7 +52792,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>医疗健康;智能科技</t>
+          <t>智能科技;医疗健康</t>
         </is>
       </c>
       <c r="D1279" t="inlineStr">
@@ -52840,7 +52840,7 @@
       </c>
       <c r="D1280" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>护理床;康复器械</t>
         </is>
       </c>
       <c r="E1280" t="inlineStr">
@@ -52917,7 +52917,7 @@
       <c r="B1282" t="inlineStr"/>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1282" t="inlineStr">
@@ -52956,7 +52956,7 @@
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1283" t="inlineStr">
@@ -52995,7 +52995,7 @@
       <c r="B1284" t="inlineStr"/>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>文娱社交;智能科技</t>
+          <t>智能科技;文娱社交</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -53034,12 +53034,12 @@
       <c r="B1285" t="inlineStr"/>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>金融保险;智能科技</t>
         </is>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>遗产规划</t>
+          <t>遗产规划;SaaS</t>
         </is>
       </c>
       <c r="E1285" t="inlineStr">
@@ -53078,7 +53078,7 @@
       </c>
       <c r="D1286" t="inlineStr">
         <is>
-          <t>药品配送</t>
+          <t>药品配送;慢病管理</t>
         </is>
       </c>
       <c r="E1286" t="inlineStr">
@@ -53117,7 +53117,7 @@
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>眼镜</t>
+          <t>眼镜;智能硬件</t>
         </is>
       </c>
       <c r="E1287" t="inlineStr">
@@ -53242,7 +53242,7 @@
       </c>
       <c r="D1290" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>糖尿病管理;慢病管理</t>
         </is>
       </c>
       <c r="E1290" t="inlineStr">
@@ -53565,12 +53565,12 @@
       <c r="B1298" t="inlineStr"/>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>文娱社交;智能科技</t>
         </is>
       </c>
       <c r="D1298" t="inlineStr">
         <is>
-          <t>健身</t>
+          <t>健身;跌倒监测</t>
         </is>
       </c>
       <c r="E1298" t="inlineStr">
@@ -53769,7 +53769,7 @@
       </c>
       <c r="D1303" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>AI医疗;慢病管理</t>
         </is>
       </c>
       <c r="E1303" t="inlineStr">
@@ -53842,7 +53842,7 @@
       <c r="B1305" t="inlineStr"/>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>养老服务;智能科技</t>
+          <t>智能科技;养老服务</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
@@ -53920,12 +53920,12 @@
       <c r="B1307" t="inlineStr"/>
       <c r="C1307" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>智能科技;医疗健康;消费品</t>
         </is>
       </c>
       <c r="D1307" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>跌倒监测;远程医疗;智能硬件</t>
         </is>
       </c>
       <c r="E1307" t="inlineStr">
@@ -53964,7 +53964,7 @@
       </c>
       <c r="D1308" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>护工平台;居家护理</t>
         </is>
       </c>
       <c r="E1308" t="inlineStr">
@@ -54284,7 +54284,7 @@
       </c>
       <c r="D1316" t="inlineStr">
         <is>
-          <t>旅居养老</t>
+          <t>持续照料社区</t>
         </is>
       </c>
       <c r="E1316" t="inlineStr">
@@ -54322,12 +54322,12 @@
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>医疗健康;康复辅具</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>远程医疗;康复器械</t>
         </is>
       </c>
       <c r="E1317" t="inlineStr">
@@ -54582,7 +54582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54615,15 +54615,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>产业基金</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VC、Venture Capital、养老科技VC、创业投资、创投基金、医疗健康投资、老年服务VC、风险投资</t>
+          <t>产业基金、产业投资基金、私募股权基金、银发产业基金</t>
         </is>
       </c>
     </row>
@@ -54635,15 +54635,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>产业基金</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>产业基金、产业投资基金、私募股权基金、银发产业基金</t>
+          <t>VC、Venture Capital、养老科技VC、创业投资、创投基金、医疗健康投资、老年服务VC、风险投资</t>
         </is>
       </c>
     </row>
@@ -54655,15 +54655,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>养老咨询</t>
+          <t>行业媒体</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>养老咨询、养老服务咨询、养老顾问</t>
+          <t>B2C媒体、信息目录、内容媒体、媒体、数字营销、营销媒体、行业媒体、行业资讯</t>
         </is>
       </c>
     </row>
@@ -54675,7 +54675,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>养老REIT</t>
+          <t>养老咨询</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -54683,7 +54683,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> healthcare REIT、 senior housing REIT、养老REIT、养老地产REIT、医疗REIT、医疗地产信托</t>
+          <t>养老咨询、养老服务咨询、养老顾问</t>
         </is>
       </c>
     </row>
@@ -54695,15 +54695,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>养老信息平台</t>
+          <t>养老REIT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>养老信息平台、养老信息门户、养老平台、养老目录</t>
+          <t xml:space="preserve"> healthcare REIT、 senior housing REIT、养老REIT、养老地产REIT、医疗REIT、医疗地产信托</t>
         </is>
       </c>
     </row>
@@ -54715,15 +54715,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>行业媒体</t>
+          <t>养老信息平台</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B2C媒体、信息目录、内容媒体、媒体、数字营销、营销媒体、行业媒体、行业资讯</t>
+          <t>养老信息平台、养老信息门户、养老平台、养老目录</t>
         </is>
       </c>
     </row>
@@ -54750,40 +54750,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>行业展会</t>
+          <t>居家护理</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>养老展会、行业博览会、行业展会</t>
+          <t>上门照护、上门照护平台、养老护理、医养服务、医院陪护/居家护理、家庭健康服务、家庭护理、家庭护理/个人护理、居家/上门护理、居家/上门护理（家庭医疗履约）、居家/旅行照护、居家养老、居家养老/保险、居家医疗服务、居家医院平台、居家急症护理、居家护理、居家护理/家政服务、居家护理对接、居家护理服务、居家服务、居家照护、居家照护/社区托管、居家照护加盟、居家照护运营、居家输液/药房、护理服务、混合护理、老年护理、长期护理、高级护理计划</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>产业资本</t>
+          <t>养老服务</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>并购投资</t>
+          <t>适老化</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PE投资、并购基金、并购投资、影响力与并购投资、影响力投资</t>
+          <t>居家适老、无障碍适老、老年友好、适老、适老化、适老化改造咨询、适老化服务</t>
         </is>
       </c>
     </row>
@@ -54795,15 +54795,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>居家护理</t>
+          <t>改造</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>上门照护、上门照护平台、养老护理、医养服务、医院陪护/居家护理、家庭健康服务、家庭护理、家庭护理/个人护理、居家/上门护理、居家/上门护理（家庭医疗履约）、居家/旅行照护、居家养老、居家养老/保险、居家医疗服务、居家医院平台、居家急症护理、居家护理、居家护理/家政服务、居家护理对接、居家护理服务、居家服务、居家照护、居家照护/社区托管、居家照护加盟、居家照护运营、居家输液/药房、护理服务、混合护理、老年护理、长期护理、高级护理计划</t>
+          <t>居家改造、改造、环境改造</t>
         </is>
       </c>
     </row>
@@ -54815,15 +54815,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>适老化</t>
+          <t>养老运营</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>居家适老、无障碍适老、老年友好、适老、适老化、适老化改造咨询、适老化服务</t>
+          <t>养老机构运营、养老运营、养老运营商、养老连锁、养老院运营、连锁养老、连锁养老运营</t>
         </is>
       </c>
     </row>
@@ -54835,15 +54835,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>改造</t>
+          <t>上门</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>居家改造、改造、环境改造</t>
+          <t>in-home、上门、上门抽血、上门服务、上门检测、上门诊疗、到家、家庭出诊、移动医疗</t>
         </is>
       </c>
     </row>
@@ -54855,15 +54855,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>养老运营</t>
+          <t>远程护理</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>养老机构运营、养老运营、养老运营商、养老连锁、养老院运营、连锁养老、连锁养老运营</t>
+          <t>数字护理协调、虚拟护理、虚拟护理协调、虚拟护理平台、远程护理、远程护理协调</t>
         </is>
       </c>
     </row>
@@ -54875,15 +54875,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>上门</t>
+          <t>护理协调</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>in-home、上门、上门抽血、上门服务、上门检测、上门诊疗、到家、家庭出诊、移动医疗</t>
+          <t>护理协调、护理协调SaaS、护理调度、护理转介、照护转介、转诊平台</t>
         </is>
       </c>
     </row>
@@ -54895,15 +54895,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>远程护理</t>
+          <t>护工平台</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>数字护理协调、虚拟护理、虚拟护理协调、虚拟护理平台、远程护理、远程护理协调</t>
+          <t>护工平台、护工撮合、照护匹配</t>
         </is>
       </c>
     </row>
@@ -54915,15 +54915,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>护理协调</t>
+          <t>持续照料社区</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>护理协调、护理协调SaaS、护理调度、护理转介、照护转介、转诊平台</t>
+          <t>CCRC、持续照料社区、持续照料退休社区</t>
         </is>
       </c>
     </row>
@@ -54935,15 +54935,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>护工平台</t>
+          <t>康养地产</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>护工平台、护工撮合、照护匹配</t>
+          <t>养老REITS、养老不动产、养老公寓开发、养老物业、养老社区开发、康养地产、持有型养老</t>
         </is>
       </c>
     </row>
@@ -54955,15 +54955,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>康养地产</t>
+          <t>家政生活服务</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>养老REITS、养老不动产、养老公寓开发、养老物业、养老社区开发、康养地产、持有型养老</t>
+          <t>上门理发、代购、保姆、保洁、家政服务、家政生活服务、家电维修、居家保洁</t>
         </is>
       </c>
     </row>
@@ -54975,15 +54975,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>家政生活服务</t>
+          <t>养老机构</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>上门理发、代购、保姆、保洁、家政服务、家政生活服务、家电维修、居家保洁</t>
+          <t>养护院、养老机构、养老机构SaaS、养老院、养老院中介、托老院、护理院、护理院运营商、敬老院、机构养老、照护机构</t>
         </is>
       </c>
     </row>
@@ -54995,15 +54995,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>持续照料社区</t>
+          <t>专业护理</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CCRC、持续照料社区、持续照料退休社区</t>
+          <t>skilled nursing、专业护理、专业级护理、二便护理、医疗护理、吞咽障碍、呼吸障碍、咀嚼障碍、尿失禁/机器人、护士、护工、院内陪护</t>
         </is>
       </c>
     </row>
@@ -55015,15 +55015,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>养老机构</t>
+          <t>养老人才培训</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>养护院、养老机构、养老机构SaaS、养老院、养老院中介、托老院、护理院、护理院运营商、敬老院、机构养老、照护机构</t>
+          <t>养老人才培训、养老护理培训、照护人才培训</t>
         </is>
       </c>
     </row>
@@ -55035,15 +55035,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>专业护理</t>
+          <t>护理者支持</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>skilled nursing、专业护理、专业级护理、二便护理、医疗护理、吞咽障碍、呼吸障碍、咀嚼障碍、尿失禁/机器人、护士、护工、院内陪护</t>
+          <t>家属照护支持、护理者支持、照护者支持</t>
         </is>
       </c>
     </row>
@@ -55055,15 +55055,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>养老人才培训</t>
+          <t>陪诊</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>养老人才培训、养老护理培训、照护人才培训</t>
+          <t>医院陪护、就医陪同、就医陪诊、就诊陪同、陪同就医、陪诊、陪诊服务</t>
         </is>
       </c>
     </row>
@@ -55075,75 +55075,75 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>护理者支持</t>
+          <t>殡葬服务</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>家属照护支持、护理者支持、照护者支持</t>
+          <t>殡仪服务、殡葬服务、生命礼仪</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>医疗健康</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>陪诊</t>
+          <t>慢病管理</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>医院陪护、就医陪同、就医陪诊、就诊陪同、陪同就医、陪诊、陪诊服务</t>
+          <t>AI慢病管理、专科慢病管理、复杂疾病、慢性病、慢性病管理、慢病数字化、慢病数字管理、慢病管理、慢病管理SaaS、数字慢病管理、糖尿病、肾脏病管理、高血压管理</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>医疗健康</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>旅居养老</t>
+          <t>远程医疗</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>候鸟养老、度假养老、异地养老、旅居养老、旅居康养、旅游养老、老年旅居</t>
+          <t>RPM、互联网医疗、医养结合、在线诊疗、居家医疗AI平台、虚拟、虚拟/面对面、虚拟健康、虚拟咨询、虚拟监护、远程医疗、远程患者照护、远程检查、远程照护、远程监控、远程营养</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>养老服务</t>
+          <t>医疗健康</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>殡葬服务</t>
+          <t>认知训练</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>殡仪服务、殡葬服务、生命礼仪</t>
+          <t>脑力训练、认知训练</t>
         </is>
       </c>
     </row>
@@ -55155,15 +55155,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>认知训练</t>
+          <t>认知数字疗法</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>脑力训练、认知训练</t>
+          <t>数字认知训练、认知数字治疗、认知数字疗法</t>
         </is>
       </c>
     </row>
@@ -55175,15 +55175,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>慢病管理</t>
+          <t>健康服务平台</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AI慢病管理、专科慢病管理、复杂疾病、慢性病、慢性病管理、慢病数字化、慢病数字管理、慢病管理、慢病管理SaaS、数字慢病管理、糖尿病、肾脏病管理、高血压管理</t>
+          <t>健康服务平台、医疗健康平台</t>
         </is>
       </c>
     </row>
@@ -55195,15 +55195,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>认知数字疗法</t>
+          <t>诊所</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>数字认知训练、认知数字治疗、认知数字疗法</t>
+          <t>clinic、医生集团、看病、社区诊所、诊所、诊所集团、连锁诊所、门诊</t>
         </is>
       </c>
     </row>
@@ -55215,15 +55215,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>远程医疗</t>
+          <t>护士上门</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RPM、互联网医疗、医养结合、在线诊疗、居家医疗AI平台、虚拟、虚拟/面对面、虚拟健康、虚拟咨询、虚拟监护、远程医疗、远程患者照护、远程检查、远程照护、远程监控、远程营养</t>
+          <t>护士上门、护士到家</t>
         </is>
       </c>
     </row>
@@ -55235,15 +55235,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>健康服务平台</t>
+          <t>药品</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>健康服务平台、医疗健康平台</t>
+          <t>OTC药品、中医药、中成药、中药、创新药、制药、化学药、医药、生物制药、药业、药企、药品</t>
         </is>
       </c>
     </row>
@@ -55255,15 +55255,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>诊所</t>
+          <t>安宁疗护</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>clinic、医生集团、看病、社区诊所、诊所、诊所集团、连锁诊所、门诊</t>
+          <t>临终关怀、安宁疗护、缓和医疗</t>
         </is>
       </c>
     </row>
@@ -55275,15 +55275,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>护士上门</t>
+          <t>远程监护</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>护士上门、护士到家</t>
+          <t>远程健康监护、远程监护</t>
         </is>
       </c>
     </row>
@@ -55295,15 +55295,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>安宁疗护</t>
+          <t>体检筛查</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>临终关怀、安宁疗护、缓和医疗</t>
+          <t>checkup、体检、体检筛查、健康筛查、全面体检、早筛、生物标志物追踪、筛查、老化诊断、血液生物标志</t>
         </is>
       </c>
     </row>
@@ -55315,15 +55315,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>药品</t>
+          <t>睡眠监测</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OTC药品、中医药、中成药、中药、创新药、制药、化学药、医药、生物制药、药业、药企、药品</t>
+          <t>睡眠健康、睡眠监测、睡眠追踪</t>
         </is>
       </c>
     </row>
@@ -55335,15 +55335,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>远程监护</t>
+          <t>更年期</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>远程健康监护、远程监护</t>
+          <t>围绝经期、女性更年期、更年期、更年期健康、绝经期</t>
         </is>
       </c>
     </row>
@@ -55355,15 +55355,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>体检筛查</t>
+          <t>康复医疗</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>checkup、体检、体检筛查、健康筛查、全面体检、早筛、生物标志物追踪、筛查、老化诊断、血液生物标志</t>
+          <t>AR神经康复、养老康复、可穿戴康复、居家康复/远程康复、康复医疗、康复设备、手部康复、数字康复、数字治疗、数字疗法、智能康复、神经康复、肿瘤康复、脑机接口康复、运动康复</t>
         </is>
       </c>
     </row>
@@ -55375,15 +55375,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>睡眠监测</t>
+          <t>居家医疗</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>睡眠健康、睡眠监测、睡眠追踪</t>
+          <t>居家医疗、居家医疗护理</t>
         </is>
       </c>
     </row>
@@ -55395,15 +55395,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>更年期</t>
+          <t>AI医疗</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>围绝经期、女性更年期、更年期、更年期健康、绝经期</t>
+          <t>AI医疗、AI医疗代理、AI医疗客服、AI医疗解决方案、AI数字健康平台、AI辅助诊断、医学影像AI、医疗AI</t>
         </is>
       </c>
     </row>
@@ -55415,15 +55415,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>康复医疗</t>
+          <t>心理健康</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AR神经康复、养老康复、可穿戴康复、居家康复/远程康复、康复医疗、康复设备、手部康复、数字康复、数字治疗、数字疗法、智能康复、神经康复、肿瘤康复、脑机接口康复、运动康复</t>
+          <t>VR培训、VR疗法、孤独干预、心理健康、心理健康服务、心理咨询、抑郁、焦虑/抑郁、睡眠CBT、睡眠呼吸、睡眠诊断、神经助眠、精神健康、行为激活</t>
         </is>
       </c>
     </row>
@@ -55435,15 +55435,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>居家医疗</t>
+          <t>用药提醒</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>居家医疗、居家医疗护理</t>
+          <t>服药提醒、用药提醒、用药通知</t>
         </is>
       </c>
     </row>
@@ -55455,15 +55455,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AI医疗</t>
+          <t>神经调控</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI医疗、AI医疗代理、AI医疗客服、AI医疗解决方案、AI数字健康平台、AI辅助诊断、医学影像AI、医疗AI</t>
+          <t>神经刺激、神经调控、脑神经调控</t>
         </is>
       </c>
     </row>
@@ -55475,15 +55475,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>SDOH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VR培训、VR疗法、孤独干预、心理健康、心理健康服务、心理咨询、抑郁、焦虑/抑郁、睡眠CBT、睡眠呼吸、睡眠诊断、神经助眠、精神健康、行为激活</t>
+          <t>AI社会护理、SDOH、SODH、支持性护理、社会决定因素、社会初级保健、社会护理网络</t>
         </is>
       </c>
     </row>
@@ -55495,15 +55495,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>用药提醒</t>
+          <t>健康管理</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>服药提醒、用药提醒、用药通知</t>
+          <t>MSK疾病、个性化健康项目、个性化治疗平台、中医、价值型医疗、体检管理、健康养生、健康平台API、健康服务、健康档案、健康管理、健康评估、健康追踪、初级/专科诊所、医保、医疗数字化、医疗服务商、医疗编码、家庭健康、家庭健康/临终关怀、数字健康、活力康养、物理治疗、疾病预测、管理式健康、综合医疗、老年医疗、肌肉骨骼护理、预防性护理、高端护理计划</t>
         </is>
       </c>
     </row>
@@ -55515,15 +55515,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>神经调控</t>
+          <t>认知症</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>神经刺激、神经调控、脑神经调控</t>
+          <t>memory care、失智照护、病情早筛、痴呆照护、痴呆症、神经退化、神经退行性疾病、神经退行性疾病药物、老年痴呆、认知健康、认知症、认知症产品、认知症照护、认知症照护支持、认知障碍、记忆护理、阿尔茨海默、阿尔茨海默照护、阿尔茨海默药</t>
         </is>
       </c>
     </row>
@@ -55535,15 +55535,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SDOH</t>
+          <t>抗衰老药物</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI社会护理、SDOH、SODH、支持性护理、社会决定因素、社会初级保健、社会护理网络</t>
+          <t>抗衰老药物、抗衰药、长寿药</t>
         </is>
       </c>
     </row>
@@ -55555,15 +55555,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>健康管理</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MSK疾病、个性化健康项目、个性化治疗平台、中医、价值型医疗、体检管理、健康养生、健康平台API、健康服务、健康档案、健康管理、健康评估、健康追踪、初级/专科诊所、医保、医疗数字化、医疗服务商、医疗编码、家庭健康、家庭健康/临终关怀、数字健康、活力康养、物理治疗、疾病预测、管理式健康、综合医疗、老年医疗、肌肉骨骼护理、预防性护理、高端护理计划</t>
+          <t>医疗器械、医疗用品、医疗设备、家用医疗、家用医疗设备(HME)、数字药房、病炊配送</t>
         </is>
       </c>
     </row>
@@ -55575,15 +55575,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>认知症</t>
+          <t>药品配送</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>memory care、失智照护、病情早筛、痴呆照护、痴呆症、神经退化、神经退行性疾病、神经退行性疾病药物、老年痴呆、认知健康、认知症、认知症产品、认知症照护、认知症照护支持、认知障碍、记忆护理、阿尔茨海默、阿尔茨海默照护、阿尔茨海默药</t>
+          <t>药品到家、药品配送、送药服务</t>
         </is>
       </c>
     </row>
@@ -55595,15 +55595,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>抗衰老药物</t>
+          <t>认知筛查</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>抗衰老药物、抗衰药、长寿药</t>
+          <t>认知功能筛查、认知筛查</t>
         </is>
       </c>
     </row>
@@ -55615,15 +55615,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>糖尿病管理</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>医疗器械、医疗用品、医疗设备、家用医疗、家用医疗设备(HME)、数字药房、病炊配送</t>
+          <t>糖尿病照护、糖尿病管理、血糖管理</t>
         </is>
       </c>
     </row>
@@ -55635,15 +55635,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>药品配送</t>
+          <t>居家康复</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>药品到家、药品配送、送药服务</t>
+          <t>上门康复、居家复健、居家康复</t>
         </is>
       </c>
     </row>
@@ -55655,15 +55655,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>认知筛查</t>
+          <t>用药管理</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>认知功能筛查、认知筛查</t>
+          <t>处方管理、用药依从、用药助手、用药管理、药物管理</t>
         </is>
       </c>
     </row>
@@ -55675,15 +55675,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>糖尿病管理</t>
+          <t>护士派遣</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>糖尿病照护、糖尿病管理、血糖管理</t>
+          <t>临床护士配置、护士外派、护士派遣</t>
         </is>
       </c>
     </row>
@@ -55695,15 +55695,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>居家康复</t>
+          <t>视觉辅助</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>上门康复、居家复健、居家康复</t>
+          <t>低视力辅助、视觉辅助、视觉辅助设备</t>
         </is>
       </c>
     </row>
@@ -55715,15 +55715,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>用药管理</t>
+          <t>中医养生</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>处方管理、用药依从、用药助手、用药管理、药物管理</t>
+          <t>中医保健、中医养生、中医理疗养生</t>
         </is>
       </c>
     </row>
@@ -55735,15 +55735,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>护士派遣</t>
+          <t>阿尔茨海默药物</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>临床护士配置、护士外派、护士派遣</t>
+          <t>AD药物、抗痴呆药物、阿尔茨海默药物</t>
         </is>
       </c>
     </row>
@@ -55755,95 +55755,95 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>视觉辅助</t>
+          <t>智能药盒</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>低视力辅助、视觉辅助、视觉辅助设备</t>
+          <t>智能药盒、智能药箱、电子药盒</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中医养生</t>
+          <t>康复器械</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中医保健、中医养生、中医理疗养生</t>
+          <t>康复器材、康复器械、康复辅助器具、理疗器械、辅助器具、适老辅具</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>阿尔茨海默药物</t>
+          <t>助听器</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AD药物、抗痴呆药物、阿尔茨海默药物</t>
+          <t>助听、助听器、助听设备、可穿戴助听、听力设备、听力评估、听力验配、听觉辅具、听觉障碍、感官辅助</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>智能药盒</t>
+          <t>助行器</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>智能药盒、智能药箱、电子药盒</t>
+          <t>助行、助行器、助行器具、助行辅具、拐杖、无障碍辅具、移位机、行动辅具、行动辅助、行走辅助</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>医疗健康</t>
+          <t>康复辅具</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>就医导航</t>
+          <t>外骨骼</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>医疗导航平台、就医导航、就医导诊</t>
+          <t>可穿戴外骨骼、外骨骼、外骨骼机器人</t>
         </is>
       </c>
     </row>
@@ -55855,15 +55855,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>康复器械</t>
+          <t>轮椅</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>康复器材、康复器械、康复辅助器具、理疗器械、辅助器具、适老辅具</t>
+          <t>wheelchair、手动轮椅、智能轮椅、电动轮椅、轮椅、轮椅车</t>
         </is>
       </c>
     </row>
@@ -55875,15 +55875,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>助听器</t>
+          <t>护理床</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>助听、助听器、助听设备、可穿戴助听、听力设备、听力评估、听力验配、听觉辅具、听觉障碍、感官辅助</t>
+          <t>养老床、家用护理床、护理床、电动床、翻身床</t>
         </is>
       </c>
     </row>
@@ -55895,115 +55895,115 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>助行器</t>
+          <t>助听辅具</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>助行、助行器、助行器具、助行辅具、拐杖、无障碍辅具、移位机、行动辅具、行动辅助、行走辅助</t>
+          <t>助听辅具、听力辅助器具</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>外骨骼</t>
+          <t>陪伴社交</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>可穿戴外骨骼、外骨骼、外骨骼机器人</t>
+          <t>情感陪伴、陪伴社交、陪聊陪伴</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>轮椅</t>
+          <t>文娱</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>wheelchair、手动轮椅、智能轮椅、电动轮椅、轮椅、轮椅车</t>
+          <t>兴趣社区、兴趣课程、内容平台、广场舞、文化、文化娱乐、文娱、短视频、老年兴趣、老年文娱、老年音乐、银发文娱</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>护理床</t>
+          <t>兴趣社群</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>养老床、家用护理床、护理床、电动床、翻身床</t>
+          <t>兴趣社交群、兴趣社群、银发兴趣圈</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>助听辅具</t>
+          <t>健身</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>助听辅具、听力辅助器具</t>
+          <t>AI锻炼、健身、在线锻炼、居家健身、椅子健身、老年健身、老年运动、运动健康</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>康复辅具</t>
+          <t>文娱社交</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>听力训练</t>
+          <t>教育</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>听力康复、听力训练、听力锻炼、听觉康复、听觉康复训练、听觉训练</t>
+          <t>兴趣学习、教育、教育+养老、线上学习、老年学校、老年教育、老年教育/兴趣社区</t>
         </is>
       </c>
     </row>
@@ -56015,15 +56015,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>陪伴社交</t>
+          <t>旅游</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>情感陪伴、陪伴社交、陪聊陪伴</t>
+          <t>康养旅居、旅游、无障碍旅游、老年旅游、银发旅游、银发旅游/康养旅居</t>
         </is>
       </c>
     </row>
@@ -56035,15 +56035,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>文娱</t>
+          <t>资讯门户</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>兴趣社区、兴趣课程、内容平台、广场舞、文化、文化娱乐、文娱、短视频、老年兴趣、老年文娱、老年音乐、银发文娱</t>
+          <t>资讯门户、银发门户</t>
         </is>
       </c>
     </row>
@@ -56055,15 +56055,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>兴趣社群</t>
+          <t>短视频直播</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>兴趣社交群、兴趣社群、银发兴趣圈</t>
+          <t>中老年短视频、短视频直播、银发直播</t>
         </is>
       </c>
     </row>
@@ -56075,15 +56075,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>健身</t>
+          <t>相亲</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AI锻炼、健身、在线锻炼、居家健身、椅子健身、老年健身、老年运动、运动健康</t>
+          <t>婚恋、相亲、相亲平台、老人相亲、老年婚恋、老年相亲、银发相亲</t>
         </is>
       </c>
     </row>
@@ -56095,15 +56095,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>就业</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>兴趣学习、教育、教育+养老、线上学习、老年学校、老年教育、老年教育/兴趣社区</t>
+          <t>中老年招聘、就业、招聘、灵活就业、灵活用工、第二职业、老年就业、职业中断、重返职场、银发就业、银发招聘</t>
         </is>
       </c>
     </row>
@@ -56115,15 +56115,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>旅游</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>康养旅居、旅游、无障碍旅游、老年旅游、银发旅游、银发旅游/康养旅居</t>
+          <t>社区、社区中心、老年社区活动、邻里社区</t>
         </is>
       </c>
     </row>
@@ -56135,895 +56135,635 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>资讯门户</t>
+          <t>邻里社交</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>资讯门户、银发门户</t>
+          <t>社区社交、邻里圈、邻里社交</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>短视频直播</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>中老年短视频、短视频直播、银发直播</t>
+          <t>SaaS、养老系统SaaS、软件即服务</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>相亲</t>
+          <t>跌倒监测</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>婚恋、相亲、相亲平台、老人相亲、老年婚恋、老年相亲、银发相亲</t>
+          <t>AI防跌倒、PERS、摔倒监测、跌倒/行为监测、跌倒检测、跌倒监测、跌倒预警、防跌倒、防跌监测</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>就业</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>中老年招聘、就业、招聘、灵活就业、灵活用工、第二职业、老年就业、职业中断、重返职场、银发就业、银发招聘</t>
+          <t xml:space="preserve"> companion robot、AI语音护理记录、云端机器人、人形机器人康养应用、具身养老机器人、具身智能通用平台、养老机器人、养老陪伴人形机器人、医疗服务机器人、医疗机器人、医院机器人、居家服务机器人、康养机器人、康复机器人、护理机器人、护理自动化、日常辅助机器人、服务机器人、机器人、机器人关节模组、治疗机器人、老年机器人、训练机器人、通用具身智能大模型、配送机器人、陪伴机器人</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>社区、社区中心、老年社区活动、邻里社区</t>
+          <t>AI、AI人口健康、AI健康、AI合规平台、AI图像分析、AI技术、AI科技、AI视觉照护、AI语音伴侣、AI调度、AI辅助、AI运营自动化、AI预测、AI饮食计划、LLM、人工智能、具身智能、大模型、智能体、智能算法、机器学习、神经科技、算法、计算机视觉</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>邻里社交</t>
+          <t>人形机器人</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>社区社交、邻里圈、邻里社交</t>
+          <t>人形机器人、类人机器人</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>智能科技</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>广场舞社交</t>
+          <t>紧急呼叫</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>广场舞社交、广场舞社群、舞友社交</t>
+          <t>SOS呼叫、紧急呼叫、紧急呼救</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>文娱社交</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>活动社交</t>
+          <t>智能硬件</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>活动社交、活动陪伴、龄动社交</t>
+          <t>AI智能温控床垫、AI监测平台、AR、具身导航、养老生活云、智能坐垫、智能家庭、智能家庭App、智能床系统、智能戒指、智能灯、智能烹饪、智能硬件、智能药丸分配器、智能遥控、智能马桶、硬件+服务、穿戴戒指、老人平板、适老化智能硬件、配药</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>美妆护肤</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SaaS、养老系统SaaS、软件即服务</t>
+          <t>美妆护肤、老年美妆</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> companion robot、AI语音护理记录、云端机器人、人形机器人康养应用、具身养老机器人、具身智能通用平台、养老机器人、养老陪伴人形机器人、医疗服务机器人、医疗机器人、医院机器人、居家服务机器人、康养机器人、康复机器人、护理机器人、护理自动化、日常辅助机器人、服务机器人、机器人、机器人关节模组、治疗机器人、老年机器人、训练机器人、通用具身智能大模型、配送机器人、陪伴机器人</t>
+          <t>服装、服装鞋帽、老年服饰、老年鞋、自适应鞋、鞋子、鞋服</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>跌倒监测</t>
+          <t>尿失禁</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AI防跌倒、PERS、摔倒监测、跌倒/行为监测、跌倒检测、跌倒监测、跌倒预警、防跌倒、防跌监测</t>
+          <t>incontinence、tena、尿失禁、添宁、漏尿、膀胱渗漏</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>个人护理</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AI、AI人口健康、AI健康、AI合规平台、AI图像分析、AI技术、AI科技、AI视觉照护、AI语音伴侣、AI调度、AI辅助、AI运营自动化、AI预测、AI饮食计划、LLM、人工智能、具身智能、大模型、智能体、智能算法、机器学习、神经科技、算法、计算机视觉</t>
+          <t>个人卫生、个人护理、个护、假发、头皮修护、头皮护理、抗衰护肤、日用、染发剂、男士护肤、皮肤长寿、老年护肤</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>人形机器人</t>
+          <t>纸尿裤</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>人形机器人、类人机器人</t>
+          <t>尿不湿、成人尿裤、护理垫、拉拉裤、纸尿裤</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>智能科技</t>
+          <t>消费品</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>紧急呼叫</t>
+          <t>眼镜</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SOS呼叫、紧急呼叫、紧急呼救</t>
+          <t>AR字幕眼镜、人工视网膜、眼科、眼镜、老花眼、老花镜、自动调节眼镜、视力检测、视力测试、视觉健康、视觉障碍</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>渠道零售</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>智能硬件</t>
+          <t>零售</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AI智能温控床垫、AI监测平台、AR、具身导航、养老生活云、智能坐垫、智能家庭、智能家庭App、智能床系统、智能戒指、智能灯、智能烹饪、智能硬件、智能药丸分配器、智能遥控、智能马桶、硬件+服务、穿戴戒指、老人平板、适老化智能硬件、配药</t>
+          <t>代工厂、会员营销、实体零售、特殊渠道、私域渠道、线下渠道、线下零售、银发零售、门店零售、零售</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>渠道零售</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>美妆护肤</t>
+          <t>电商</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>美妆护肤、老年美妆</t>
+          <t>电商、电商平台、电商购物、电子商务、网上购物、网购</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>渠道零售</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>尿失禁</t>
+          <t>垂直电商</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>incontinence、tena、尿失禁、添宁、漏尿、膀胱渗漏</t>
+          <t>垂直电商、垂类电商、细分品类电商</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>服装、服装鞋帽、老年服饰、老年鞋、自适应鞋、鞋子、鞋服</t>
+          <t>Medicare Advantage、保险、保险(MA)/初级保健、保险助手、保险服务、保险经纪、医疗保险、医疗保险+诊所、医疗保险计划、医疗险</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>个人护理</t>
+          <t>金融理财</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>个人卫生、个人护理、个护、假发、头皮修护、头皮护理、抗衰护肤、日用、染发剂、男士护肤、皮肤长寿、老年护肤</t>
+          <t>理财、财务规划、财富管理、资产配置、金融理财</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>纸尿裤</t>
+          <t>保险科技</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>尿不湿、成人尿裤、护理垫、拉拉裤、纸尿裤</t>
+          <t>InsurTech、保险科技、保险科技平台、保险科技服务、保险科技解决方案</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>消费品</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>眼镜</t>
+          <t>遗产规划</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AR字幕眼镜、人工视网膜、眼科、眼镜、老花眼、老花镜、自动调节眼镜、视力检测、视力测试、视觉健康、视觉障碍</t>
+          <t>财富传承、身后事规划、遗产规划、遗产记录</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>金融保险</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>电商</t>
+          <t>长护险经办</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>电商、电商平台、电商购物、电子商务、网上购物、网购</t>
+          <t>长护险、长护险经办、长期护理险经办</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>零售</t>
+          <t>保健品</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>代工厂、会员营销、实体零售、特殊渠道、私域渠道、线下渠道、线下零售、银发零售、门店零售、零售</t>
+          <t>保健、保健产品、保健品、保健品&amp;OTC、保健营销、养生、美容保健</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>垂直电商</t>
+          <t>营养食品</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>垂直电商、垂类电商、细分品类电商</t>
+          <t>个性化补充剂、婴儿营养、婴儿配方奶粉、微生态、老年膳食、老年营养/功能食品、老年食品、膳食、膳食计划、营养、营养/生物技术、营养保健品、营养咨询、营养品、营养平台、营养营销、营养食品、补充剂、补剂、银发食品、食品科技、食品解决方案、骨胶原</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>电视购物</t>
+          <t>维生素矿物质</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>电视购物、电视购物台、视购</t>
+          <t>矿物质补充剂、维生素矿物质、维生素补充剂</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>私域电商</t>
+          <t>膳食配送</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>社群团购、私域电商</t>
+          <t>膳食配送、送餐服务、餐食配送</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>渠道零售</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>电商服务</t>
+          <t>个性化营养</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>电商代运营、电商服务、电商赋能</t>
+          <t>个性化营养、定制营养、营养定制</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>功能性食品</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Medicare Advantage、保险、保险(MA)/初级保健、保险助手、保险服务、保险经纪、医疗保险、医疗保险+诊所、医疗保险计划、医疗险</t>
+          <t>功能型食品、功能性食品、机能食品</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>金融服务</t>
+          <t>中药滋补</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>企业金融、支付金融、资金管理、金融服务、金融解决方案</t>
+          <t>中草药保健、中药滋补、中药滋补品、中药调养、滋补中药、滋补养生</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>金融理财</t>
+          <t>养老膳食</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>理财、财务规划、财富管理、资产配置、金融理财</t>
+          <t>养老膳食、养老餐食、老年餐</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>保险科技</t>
+          <t>膳食补充剂</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InsurTech、保险科技、保险科技平台、保险科技服务、保险科技解决方案</t>
+          <t>膳食营养、膳食补充剂、营养补充剂</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>金融保险</t>
+          <t>食品营养</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>遗产规划</t>
+          <t>特医食品</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>财富传承、身后事规划、遗产规划、遗产记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>金融保险</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>长护险经办</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>5</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>长护险、长护险经办、长期护理险经办</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>保健品</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>15</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>保健、保健产品、保健品、保健品&amp;OTC、保健营销、养生、美容保健</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>营养食品</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>14</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>个性化补充剂、婴儿营养、婴儿配方奶粉、微生态、老年膳食、老年营养/功能食品、老年食品、膳食、膳食计划、营养、营养/生物技术、营养保健品、营养咨询、营养品、营养平台、营养营销、营养食品、补充剂、补剂、银发食品、食品科技、食品解决方案、骨胶原</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>维生素矿物质</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>14</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>矿物质补充剂、维生素矿物质、维生素补充剂</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>膳食配送</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>10</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>膳食配送、送餐服务、餐食配送</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>个性化营养</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>9</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>个性化营养、定制营养、营养定制</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>功能性食品</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>6</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>功能型食品、功能性食品、机能食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>中药滋补</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>6</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>中草药保健、中药滋补、中药滋补品、中药调养、滋补中药、滋补养生</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>养老膳食</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>6</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>养老膳食、养老餐食、老年餐</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>膳食补充剂</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>6</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>膳食营养、膳食补充剂、营养补充剂</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>特医食品</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>5</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
           <t>临床营养、特医、特医配方、特医食品</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>益生菌肠道</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>3</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>益生菌肠道、肠道健康菌</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>食品营养</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>骨关节钙</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>3</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>钙补充剂、骨关节钙</t>
         </is>
       </c>
     </row>
